--- a/Alumni_System/generated_token.xlsx
+++ b/Alumni_System/generated_token.xlsx
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" outlineLevelRow="0" zeroHeight="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" style="4" width="19.85"/>
@@ -582,6 +582,41 @@
         <v>43863.79355396315</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Just Check</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>importanthacknotice@gmail.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MITAOE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>86rguzz696fx</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>final_result</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>43863.98879850702</v>
+      </c>
+    </row>
     <row customHeight="1" ht="12.8" r="1048575" s="5"/>
     <row customHeight="1" ht="12.8" r="1048576" s="5"/>
   </sheetData>
